--- a/docs/StructureDefinition-IbActionTypes3501.xlsx
+++ b/docs/StructureDefinition-IbActionTypes3501.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IbActionTypes3501.xlsx
+++ b/docs/StructureDefinition-IbActionTypes3501.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>IbActionTypes3501.name</t>
+    <t>IbActionTypes3501.chargeCategory</t>
   </si>
   <si>
     <t>1</t>
@@ -257,7 +257,7 @@
 </t>
   </si>
   <si>
-    <t>NAME (-.01)</t>
+    <t>CHARGE CATEGORY (-.03)</t>
   </si>
 </sst>
 </file>
@@ -562,8 +562,8 @@
   <dimension ref="A1:AJ3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="24.421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="24.421875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.9375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.9375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -593,7 +593,7 @@
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="24.421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="33.9375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>

--- a/docs/StructureDefinition-IbActionTypes3501.xlsx
+++ b/docs/StructureDefinition-IbActionTypes3501.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IbActionTypes3501.xlsx
+++ b/docs/StructureDefinition-IbActionTypes3501.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IbActionTypes3501.xlsx
+++ b/docs/StructureDefinition-IbActionTypes3501.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IbActionTypes3501.xlsx
+++ b/docs/StructureDefinition-IbActionTypes3501.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IbActionTypes3501.xlsx
+++ b/docs/StructureDefinition-IbActionTypes3501.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IbActionTypes3501.xlsx
+++ b/docs/StructureDefinition-IbActionTypes3501.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IbActionTypes3501.xlsx
+++ b/docs/StructureDefinition-IbActionTypes3501.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
